--- a/05_Figures/Proteome_acute/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Proteome_acute/F1_Overview/c_data/f1_overview.xlsx
@@ -104,16 +104,16 @@
     <t>Participant identifier.</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>hr_lr</t>
+  </si>
+  <si>
+    <t>The study's HR or LR label, shown beside a cluster grouping's own group.</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
-    <t>Group the row belongs to (HR, LR, Hi, Lo, C1, C2), or a group cell such as HR_T1.</t>
+    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
   </si>
   <si>
     <t>cluster</t>
@@ -200,7 +200,7 @@
     <t>Time window or pairing: training (T2 - T1), acute (T3 - T2), baseline (T1 level against later change), baseline_level, post_level, post_bout_level (a level against trait levels); all or a time point in PERMANOVA.</t>
   </si>
   <si>
-    <t>arms</t>
+    <t>groups</t>
   </si>
   <si>
     <t>Groups included in the test.</t>
@@ -821,7 +821,7 @@
     <t>03_Group_comparisons/Proteome_acute/c_data/02_protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>7a034c8be81b13e52c8a7efab2804be1</t>
+    <t>d4ddfcc86c2c3c0610b882523e50b5b7</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -845,13 +845,13 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>02_Groups/Proteome_acute/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>d80f6cb54482b3e0167044b56804f223</t>
+    <t>88f1830b45c8bd84a3abb358f54e130c</t>
   </si>
   <si>
     <t>design</t>
@@ -860,7 +860,7 @@
     <t>03_Group_comparisons/Proteome_acute/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>e867d7c61225d2e1a8e90858506efcc1</t>
+    <t>2b09cccaba028e990db41554d1d0d983</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -2833,10 +2833,10 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2866,10 +2866,10 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4025,7 +4025,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>50</v>
@@ -4926,7 +4926,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>50</v>
@@ -5706,7 +5706,7 @@
         <v>186</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>192</v>
@@ -5732,7 +5732,7 @@
         <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>129</v>
@@ -5758,7 +5758,7 @@
         <v>186</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>155</v>
@@ -5784,7 +5784,7 @@
         <v>186</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>171</v>
